--- a/public/downloads/SharadaAdsorption2019.xlsx
+++ b/public/downloads/SharadaAdsorption2019.xlsx
@@ -1578,16 +1578,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1014721506093558</v>
+        <v>-0.09867418674333095</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5277810598633361</v>
+        <v>0.5268484052413278</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04781255613185038</v>
+        <v>0.04725296335864541</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.01292621460007695</v>
+        <v>-0.1881579977465719</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
@@ -2282,7 +2282,7 @@
         <v>0.4755884648307074</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3619014542093555</v>
+        <v>0.3268550975800565</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -2964,16 +2964,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2033172142089633</v>
+        <v>0.2160085362421986</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.05654755941615482</v>
+        <v>0.05361175268193966</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05654755941615482</v>
+        <v>0.05361175268193966</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -3651,20 +3651,22 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>2.677218960752782</v>
+        <v>0.4133387792602292</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>3.839344767555872</v>
-      </c>
-      <c r="Q3" s="4"/>
+        <v>2.379971170519184</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09958250779098705</v>
+      </c>
       <c r="R3" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S3" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -4332,7 +4334,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.06033355560349492</v>
+        <v>-0.1352395636035055</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
@@ -4341,7 +4343,7 @@
         <v>0.9889081161165146</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09419149327185551</v>
+        <v>0.07921029167185338</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -5027,7 +5029,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1287284072880652</v>
+        <v>-0.1298606793897079</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
@@ -5036,7 +5038,7 @@
         <v>1.183398347753894</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08249706859999151</v>
+        <v>0.08227061417966297</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -5718,16 +5720,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3787194560276485</v>
+        <v>0.4281467014892613</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1190042529858972</v>
+        <v>0.1185836839635002</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1190042529858972</v>
+        <v>0.1185836839635002</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -6397,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.07055729425878354</v>
+        <v>-0.07986266724565283</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -7088,16 +7090,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3768729836053666</v>
+        <v>0.4364304358108555</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1296631351193334</v>
+        <v>0.1182219235061434</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1296631351193334</v>
+        <v>0.1182219235061434</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -7767,16 +7769,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.142583635479897</v>
+        <v>-0.09205094334049591</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4464963421145572</v>
+        <v>0.3944199186604417</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4464963421145572</v>
+        <v>0.3944199186604417</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -8422,13 +8424,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4315942428514006</v>
+        <v>0.4297318909299608</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1898271655098589</v>
+        <v>0.1887097543569951</v>
       </c>
       <c r="J3" s="4">
-        <v>0.7135028640957717</v>
+        <v>0.7127200223631291</v>
       </c>
       <c r="K3" s="4">
         <v>61.515495086924</v>
@@ -8472,13 +8474,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.3508450200068391</v>
+        <v>0.3434769841991852</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3603359495097673</v>
+        <v>0.352534499831075</v>
       </c>
       <c r="J4" s="4">
-        <v>0.4149853398310578</v>
+        <v>0.4138310220138553</v>
       </c>
       <c r="K4" s="4">
         <v>71.4399092970522</v>
@@ -8522,13 +8524,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.3396375550806083</v>
+        <v>0.3099333206501424</v>
       </c>
       <c r="I5" s="4">
-        <v>0.3492830882179361</v>
+        <v>0.3178315458797957</v>
       </c>
       <c r="J5" s="4">
-        <v>0.3794990077428908</v>
+        <v>0.3432158940884954</v>
       </c>
       <c r="K5" s="4">
         <v>70.17006802721095</v>
@@ -8572,13 +8574,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.2701760773130426</v>
+        <v>0.2659269785409006</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2770236288476603</v>
+        <v>0.2746335107883304</v>
       </c>
       <c r="J6" s="4">
-        <v>0.3333323906794028</v>
+        <v>0.3321124168790656</v>
       </c>
       <c r="K6" s="4">
         <v>67.64172335600921</v>
@@ -8622,13 +8624,13 @@
         <v>5.555555555555555</v>
       </c>
       <c r="H7" s="4">
-        <v>0.9545116834764857</v>
+        <v>0.7156316299275842</v>
       </c>
       <c r="I7" s="4">
-        <v>0.7417206396046083</v>
+        <v>0.3513642136164198</v>
       </c>
       <c r="J7" s="4">
-        <v>0.9936518814423196</v>
+        <v>0.7575633385813521</v>
       </c>
       <c r="K7" s="4">
         <v>67.48299319727921</v>
@@ -8672,13 +8674,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.3766254695812029</v>
+        <v>0.3763145847072001</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2229851109718236</v>
+        <v>0.2228102382301971</v>
       </c>
       <c r="J8" s="4">
-        <v>0.46961895981689</v>
+        <v>0.4693080749428873</v>
       </c>
       <c r="K8" s="4">
         <v>72.66439909297054</v>
@@ -8725,10 +8727,10 @@
         <v>0.4080867085466259</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3461719192049691</v>
+        <v>0.3344898003285361</v>
       </c>
       <c r="J9" s="4">
-        <v>0.4520629359890493</v>
+        <v>0.4635977328097959</v>
       </c>
       <c r="K9" s="4">
         <v>68.73015873015909</v>
@@ -8772,13 +8774,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.307807641601978</v>
+        <v>0.3068290393572396</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3326194721345372</v>
+        <v>0.3315185446092065</v>
       </c>
       <c r="J10" s="4">
-        <v>0.336361333829129</v>
+        <v>0.3366321484359388</v>
       </c>
       <c r="K10" s="4">
         <v>68.97959183673504</v>
@@ -8804,13 +8806,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>38.88888888888889</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="C11" s="3">
         <v>22.22222222222222</v>
       </c>
       <c r="D11" s="3">
-        <v>38.88888888888889</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
@@ -8819,16 +8821,16 @@
         <v>5.555555555555555</v>
       </c>
       <c r="G11" s="3">
-        <v>33.33333333333333</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="H11" s="4">
-        <v>1.62181860625364</v>
+        <v>1.135360740574744</v>
       </c>
       <c r="I11" s="4">
-        <v>0.3770824738433264</v>
+        <v>0.261457487988185</v>
       </c>
       <c r="J11" s="4">
-        <v>1.681111041899698</v>
+        <v>1.182810448559669</v>
       </c>
       <c r="K11" s="4">
         <v>67.52834467120211</v>
@@ -8875,7 +8877,7 @@
         <v>0.6516663340568667</v>
       </c>
       <c r="I12" s="4">
-        <v>0.3424317906474676</v>
+        <v>0.337750165147467</v>
       </c>
       <c r="J12" s="4">
         <v>0.7972233667479744</v>
@@ -8925,7 +8927,7 @@
         <v>0.5775699129846841</v>
       </c>
       <c r="I13" s="4">
-        <v>0.2285973527060946</v>
+        <v>0.2285218678993184</v>
       </c>
       <c r="J13" s="4">
         <v>0.862182860024818</v>
@@ -8972,13 +8974,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.3876563925670186</v>
+        <v>0.3875162028928862</v>
       </c>
       <c r="I14" s="4">
-        <v>0.4714898007210717</v>
+        <v>0.4712603994361279</v>
       </c>
       <c r="J14" s="4">
-        <v>0.4605989990147299</v>
+        <v>0.4604625853724278</v>
       </c>
       <c r="K14" s="4">
         <v>53.48639455782275</v>
@@ -9028,7 +9030,7 @@
         <v>0.2840325615729928</v>
       </c>
       <c r="J15" s="4">
-        <v>0.2905877564857227</v>
+        <v>0.290238232472946</v>
       </c>
       <c r="K15" s="4">
         <v>75.17006802721087</v>
@@ -9072,13 +9074,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.3956050041848655</v>
+        <v>0.3917912669804689</v>
       </c>
       <c r="I16" s="4">
-        <v>0.4445326266621855</v>
+        <v>0.4392520674560977</v>
       </c>
       <c r="J16" s="4">
-        <v>0.4497413203408382</v>
+        <v>0.4492810636255741</v>
       </c>
       <c r="K16" s="4">
         <v>58.46938775510159</v>
@@ -9122,13 +9124,13 @@
         <v>5.555555555555555</v>
       </c>
       <c r="H17" s="4">
-        <v>0.7989356860618975</v>
+        <v>0.781576878243859</v>
       </c>
       <c r="I17" s="4">
-        <v>0.6726493005506168</v>
+        <v>0.6518187311689706</v>
       </c>
       <c r="J17" s="4">
-        <v>0.9957884892921912</v>
+        <v>0.9689777938003508</v>
       </c>
       <c r="K17" s="4">
         <v>74.04761904761916</v>
@@ -10363,13 +10365,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C11" s="5">
         <v>4</v>
       </c>
       <c r="D11" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5">
         <v>0</v>
@@ -10378,7 +10380,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H11" s="5">
         <v>0</v>
@@ -10825,16 +10827,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2016719039921668</v>
+        <v>-0.1849107366992087</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8223638976914041</v>
+        <v>0.8167768419270848</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06511632422812909</v>
+        <v>0.06176409076953746</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -11516,16 +11518,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.05344338513344837</v>
+        <v>-0.1197557074023337</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1580661125856864</v>
+        <v>0.1359620051627246</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1580661125856864</v>
+        <v>0.1359620051627246</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -12207,16 +12209,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3400406435436973</v>
+        <v>0.1445183074304737</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3396907716909507</v>
+        <v>0.2505780683995529</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3396907716909507</v>
+        <v>0.2505780683995529</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -12902,16 +12904,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.352446303553711</v>
+        <v>0.3142044146044327</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1510440436178366</v>
+        <v>0.1382967473014105</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1558528589734533</v>
+        <v>0.1482044811835976</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -13593,16 +13595,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>1.493300007810888</v>
+        <v>0.3281510078564764</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>2.060222732847213</v>
+        <v>1.343582572200508</v>
       </c>
       <c r="Q3" s="4">
-        <v>1.236133639708328</v>
+        <v>0.1431356469413999</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
